--- a/backend/打印模板.xlsx
+++ b/backend/打印模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\PycharmProjects\shop_system\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFD20CA6-A46F-442A-B6B3-1AAC6E0C5FE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EC445D4-E5B3-47B4-8E7C-AC0F062812AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -400,32 +400,32 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="22" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -782,10 +782,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z21"/>
+  <dimension ref="A1:Z22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.21875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="1.5546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="4.109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="6" style="1" customWidth="1"/>
     <col min="4" max="4" width="15.77734375" style="1" customWidth="1"/>
@@ -799,28 +799,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
     </row>
     <row r="2" spans="1:26" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
     </row>
     <row r="3" spans="1:26" s="2" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
@@ -1031,8 +1031,8 @@
     </row>
     <row r="12" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="13"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="28"/>
       <c r="E12" s="13"/>
       <c r="F12" s="13"/>
       <c r="G12" s="13"/>
@@ -1045,8 +1045,8 @@
     </row>
     <row r="13" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="13"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="28"/>
       <c r="E13" s="13"/>
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
@@ -1059,8 +1059,8 @@
     </row>
     <row r="14" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="13"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="28"/>
       <c r="E14" s="13"/>
       <c r="F14" s="13"/>
       <c r="G14" s="13"/>
@@ -1073,8 +1073,8 @@
     </row>
     <row r="15" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="13"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="27"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="28"/>
       <c r="E15" s="13"/>
       <c r="F15" s="13"/>
       <c r="G15" s="13"/>
@@ -1087,8 +1087,8 @@
     </row>
     <row r="16" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="13"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="28"/>
       <c r="E16" s="13"/>
       <c r="F16" s="13"/>
       <c r="G16" s="13"/>
@@ -1111,18 +1111,18 @@
       <c r="J17" s="17"/>
     </row>
     <row r="18" spans="1:26" s="4" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.25">
-      <c r="B18" s="31" t="s">
+      <c r="B18" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="32"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="31" t="str">
+      <c r="C18" s="33"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="32" t="str">
         <f>IF(I18=0,"",IF(I18&lt;0,"负","")&amp;IF(INT(I18),TEXT(INT(ABS(I18)),"[dbnum2]")&amp;"元","")&amp;IF(INT(ABS(I18)*10)-INT(ABS(I18))*10,TEXT(INT(ABS(I18)*10)-INT(ABS(I18))*10,"[dbnum2]")&amp;"角",IF(INT(ABS(I18))=ABS(I18),,"零"))&amp;IF(INT(ABS(I18)*100)-INT(ABS(I18)*10)*10,TEXT(INT(ABS(I18)*100)-INT(ABS(I18)*10)*10,"[dbnum2]")&amp;"分",IF(ROUND(ABS(I18)*100,)=0,"整","")))</f>
         <v/>
       </c>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="34"/>
       <c r="I18" s="18">
         <f>SUM(I12:I17)</f>
         <v>0</v>
@@ -1130,28 +1130,24 @@
       <c r="J18" s="19"/>
     </row>
     <row r="19" spans="1:26" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="28"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="29"/>
-      <c r="J19" s="30"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="31"/>
     </row>
     <row r="21" spans="1:26" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
-      <c r="C21" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
-      <c r="G21" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -1172,14 +1168,40 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
+    <row r="22" spans="1:26" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="1"/>
+      <c r="U22" s="1"/>
+      <c r="V22" s="1"/>
+      <c r="W22" s="1"/>
+      <c r="X22" s="1"/>
+      <c r="Y22" s="1"/>
+      <c r="Z22" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B1:J2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="D5:E5"/>
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="C15:D15"/>
@@ -1191,9 +1213,18 @@
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="E18:H18"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B1:J2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="D5:E5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.55118110236220474" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageMargins left="0.23333333333333334" right="0.23622047244094491" top="0.40833333333333333" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="148" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;9第 &amp;P 页，共 &amp;N 页</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>